--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Business-Case-Model.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Business-Case-Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chigh\flowbuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902E8DE5-4A27-4CD3-A2DC-511726BCFF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4562277-85C8-4696-AA0F-4ED70A3C0A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,13 +19,14 @@
     <sheet name="Cost" sheetId="4" r:id="rId4"/>
     <sheet name="Summary" sheetId="5" r:id="rId5"/>
     <sheet name="Baseline" sheetId="6" r:id="rId6"/>
+    <sheet name="Definitions" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="342">
   <si>
     <t>Capacity &amp; Scheduling — Business Case Model</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Size the initiative from editable drivers rather than from a fixed conclusion. Change any blue cell and every downstream number moves.</t>
   </si>
   <si>
-    <t>Colour legend</t>
+    <t>Color legend</t>
   </si>
   <si>
     <t>BLUE = an input you may edit.  BLACK = a formula, do not overwrite.  GREEN = a link to another sheet.  YELLOW FILL = unresolved or invented, must be replaced before external use.</t>
@@ -78,7 +79,7 @@
     <t>Edit blue cells only. Yellow = unresolved, replace before external use.</t>
   </si>
   <si>
-    <t>A.  ORGANISATION AND SCALE</t>
+    <t>A.  ORGANIZATION AND SCALE</t>
   </si>
   <si>
     <t>Driver</t>
@@ -153,402 +154,432 @@
     <t>Derived</t>
   </si>
   <si>
+    <t>Admissions per year, all branches (new starts of care)</t>
+  </si>
+  <si>
+    <t>600/branch x 80 (workbook). UNRESOLVED: cannot carry $549M</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Medicare 30-day payment periods per year, all branches</t>
+  </si>
+  <si>
+    <t>1,000/branch x 80 (workbook). Derived alternative is 128,000</t>
+  </si>
+  <si>
+    <t>Total visits per year</t>
+  </si>
+  <si>
+    <t>Estimate: 3,000 clinicians x ~1,000 visits</t>
+  </si>
+  <si>
+    <t>Non-episodic visits per year</t>
+  </si>
+  <si>
+    <t>Estimate from non-FFS revenue</t>
+  </si>
+  <si>
+    <t>B.  UNIT ECONOMICS</t>
+  </si>
+  <si>
+    <t>Margin per additional admission (revenue less variable cost)</t>
+  </si>
+  <si>
+    <t>8.13 workbook</t>
+  </si>
+  <si>
+    <t>Workbook</t>
+  </si>
+  <si>
+    <t>Revenue protected per avoided LUPA</t>
+  </si>
+  <si>
+    <t>Contribution per non-episodic visit</t>
+  </si>
+  <si>
+    <t>Derived: ~$150 revenue less per-visit pay and variable</t>
+  </si>
+  <si>
+    <t>Modeled</t>
+  </si>
+  <si>
+    <t>Loaded cost per scheduler</t>
+  </si>
+  <si>
+    <t>BLS home health scheduler $38,090 median x 1.43</t>
+  </si>
+  <si>
+    <t>Replacement cost per clinician</t>
+  </si>
+  <si>
+    <t>Clinician departures per branch per year (all causes)</t>
+  </si>
+  <si>
+    <t>Premium labor spend per branch per year (contract, per diem, overtime)</t>
+  </si>
+  <si>
+    <t>Annual mileage spend, network</t>
+  </si>
+  <si>
+    <t>INVENTED: 3,000 x 8,000 miles x $0.67. Replace</t>
+  </si>
+  <si>
+    <t>Invented</t>
+  </si>
+  <si>
+    <t>C.  SCENARIO DRIVERS</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Mod</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>Increase in admissions</t>
+  </si>
+  <si>
+    <t>LeanTaaS 2% acute; field service 4-15%</t>
+  </si>
+  <si>
+    <t>Fill-rate percentage points recovered (non-episodic)</t>
+  </si>
+  <si>
+    <t>Industry fill rates 88-90%</t>
+  </si>
+  <si>
+    <t>LUPA reduction, points of periods</t>
+  </si>
+  <si>
+    <t>8.13 workbook scenario drivers</t>
+  </si>
+  <si>
+    <t>Scheduler FTE released</t>
+  </si>
+  <si>
+    <t>Vendor comparable 27-44; bottom-up build 90</t>
+  </si>
+  <si>
+    <t>Share of premium labor converted to planned coverage</t>
+  </si>
+  <si>
+    <t>Clinician turnover reduction</t>
+  </si>
+  <si>
+    <t>8.13 workbook; Bergman 9.2pp worst quartile</t>
+  </si>
+  <si>
+    <t>Travel and mileage reduction</t>
+  </si>
+  <si>
+    <t>Field service 5-15%; UPS ORION 8-10%</t>
+  </si>
+  <si>
+    <t>D.  COST OF OWNERSHIP DRIVERS</t>
+  </si>
+  <si>
+    <t>Implementation and integration (one-time)</t>
+  </si>
+  <si>
+    <t>Data readiness (one-time)</t>
+  </si>
+  <si>
+    <t>Go-live productivity dip (one-time)</t>
+  </si>
+  <si>
+    <t>Software license (per year)</t>
+  </si>
+  <si>
+    <t>Internal program labor (per year)</t>
+  </si>
+  <si>
+    <t>Change management (per year)</t>
+  </si>
+  <si>
+    <t>Run and support (per year)</t>
+  </si>
+  <si>
+    <t>License is ~10% of total; internal labor ~42%</t>
+  </si>
+  <si>
+    <t>E.  BENEFIT RAMP</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Share of steady-state benefit realized</t>
+  </si>
+  <si>
+    <t>Phased rollout across ~80 branches</t>
+  </si>
+  <si>
+    <t>Outside-view benefit haircut</t>
+  </si>
+  <si>
+    <t>Set to 56% to apply the McKinsey-Oxford shortfall</t>
+  </si>
+  <si>
+    <t>F.  SCENARIO SELECTOR</t>
+  </si>
+  <si>
+    <t>Scenario driving the Summary sheet</t>
+  </si>
+  <si>
+    <t>Selected scenario</t>
+  </si>
+  <si>
+    <t>Column index (1=Min, 2=Mod, 3=Max)</t>
+  </si>
+  <si>
+    <t>Used by INDEX on the Levers pick</t>
+  </si>
+  <si>
+    <t>Selected COST scenario</t>
+  </si>
+  <si>
+    <t>Set independently of the benefit scenario. An ambitious benefit case does not require an ambitious spend case</t>
+  </si>
+  <si>
+    <t>Cost column index</t>
+  </si>
+  <si>
+    <t>Value levers — annual, at steady state</t>
+  </si>
+  <si>
+    <t>Gross of platform cost. Formulas reference Inputs; edit drivers there, not here.</t>
+  </si>
+  <si>
+    <t>Lever</t>
+  </si>
+  <si>
+    <t>Formula in words</t>
+  </si>
+  <si>
+    <t>1  Speed to answer -&gt; admissions (SOC-capable pool)</t>
+  </si>
+  <si>
+    <t>Admissions x lift x contribution per admission</t>
+  </si>
+  <si>
+    <t>2  Routine throughput and fill rate (paraprofessional pool)</t>
+  </si>
+  <si>
+    <t>Non-episodic visits x fill points x contribution per visit</t>
+  </si>
+  <si>
+    <t>3  LUPA as a scheduling gear</t>
+  </si>
+  <si>
+    <t>Periods x reduction points x revenue protected</t>
+  </si>
+  <si>
+    <t>4  Scheduler capacity released</t>
+  </si>
+  <si>
+    <t>FTE released x loaded cost</t>
+  </si>
+  <si>
+    <t>5  Premium and contract labor recovered</t>
+  </si>
+  <si>
+    <t>Branches x premium pool x recovery rate</t>
+  </si>
+  <si>
+    <t>6  Clinician retention</t>
+  </si>
+  <si>
+    <t>Branches x departures x reduction x replacement cost</t>
+  </si>
+  <si>
+    <t>7  Travel and mileage</t>
+  </si>
+  <si>
+    <t>Mileage spend x reduction rate</t>
+  </si>
+  <si>
+    <t>TOTAL, gross of platform cost</t>
+  </si>
+  <si>
+    <t>NOT YET VALUED — future-year case</t>
+  </si>
+  <si>
+    <t>8  Clinician attraction (recruiting advantage)</t>
+  </si>
+  <si>
+    <t>Not yet valued</t>
+  </si>
+  <si>
+    <t>Two mechanisms: the day-before confirmation burden moves off the clinician, and income becomes predictable. Both are recruiting arguments, not just retention ones</t>
+  </si>
+  <si>
+    <t>9  Hospice extension of the same instrument</t>
+  </si>
+  <si>
+    <t>The 8.13 workbook states four hospice mechanics need rules added, not new products</t>
+  </si>
+  <si>
+    <t>10  Authorization write-offs avoided</t>
+  </si>
+  <si>
+    <t>Unmeasured</t>
+  </si>
+  <si>
+    <t>Visits delivered outside the payer backdating window. Could be immaterial or the largest single lever</t>
+  </si>
+  <si>
+    <t>Attribution notes</t>
+  </si>
+  <si>
+    <t>- Levers 1 and 2 are separate capacity pools — SOC-capable clinicians and paraprofessionals — and are additive.</t>
+  </si>
+  <si>
+    <t>- Lever 2 is valued on the non-episodic book only. Above the LUPA floor an extra episodic visit earns no revenue.</t>
+  </si>
+  <si>
+    <t>- Lever 3 recovers only clinically indicated visits lost to operational failure. It never adds a visit to clear a threshold.</t>
+  </si>
+  <si>
+    <t>- Lever 7 counts mileage reimbursement only. Under per-visit pay the saved drive time accrues to the clinician, and converts to capacity in lever 1.</t>
+  </si>
+  <si>
+    <t>- Lever 4 excludes severance, which sits on the Cost sheet.</t>
+  </si>
+  <si>
+    <t>Cost of ownership — three years</t>
+  </si>
+  <si>
+    <t>Scenario follows the selector on Inputs B60.</t>
+  </si>
+  <si>
+    <t>Cost line</t>
+  </si>
+  <si>
+    <t>Three-year total</t>
+  </si>
+  <si>
+    <t>Implementation and integration</t>
+  </si>
+  <si>
+    <t>Data readiness</t>
+  </si>
+  <si>
+    <t>Go-live productivity dip</t>
+  </si>
+  <si>
+    <t>Software license</t>
+  </si>
+  <si>
+    <t>Internal program labor</t>
+  </si>
+  <si>
+    <t>Change management</t>
+  </si>
+  <si>
+    <t>Run and support</t>
+  </si>
+  <si>
+    <t>Severance on released scheduler roles</t>
+  </si>
+  <si>
+    <t>Assumes 3 months per released role, in year 2</t>
+  </si>
+  <si>
+    <t>TOTAL COST</t>
+  </si>
+  <si>
+    <t>Summary — net position and payback</t>
+  </si>
+  <si>
+    <t>Steady-state benefit, gross</t>
+  </si>
+  <si>
+    <t>Ramp</t>
+  </si>
+  <si>
+    <t>Outside-view haircut</t>
+  </si>
+  <si>
+    <t>Benefit realized</t>
+  </si>
+  <si>
+    <t>Total cost</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>Cumulative net</t>
+  </si>
+  <si>
+    <t>Three-year ROI</t>
+  </si>
+  <si>
+    <t>Payback</t>
+  </si>
+  <si>
+    <t>Steady-state annual benefit, by lever (selected scenario)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Read this before quoting a number</t>
+  </si>
+  <si>
+    <t>- State the four attribution conventions with any figure: gross or incremental; which revenue base; how many levers; whether config-achievable value counts.</t>
+  </si>
+  <si>
+    <t>- Set the outside-view haircut on Inputs B55 to 56% to see the McKinsey-Oxford expected case.</t>
+  </si>
+  <si>
+    <t>- Three inputs are unresolved and marked yellow. The admissions lever scales linearly with network admissions.</t>
+  </si>
+  <si>
+    <t>Baseline measurement plan</t>
+  </si>
+  <si>
+    <t>Nothing in this model can be committed until these are measured. Ordered by which lever they gate.</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>What it measures</t>
+  </si>
+  <si>
+    <t>Gates which lever</t>
+  </si>
+  <si>
+    <t>Source system</t>
+  </si>
+  <si>
+    <t>Available today</t>
+  </si>
+  <si>
+    <t>How to obtain</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
     <t>Network admissions per year</t>
   </si>
   <si>
-    <t>600/branch x 80 (workbook). UNRESOLVED: cannot carry $549M</t>
-  </si>
-  <si>
-    <t>Weak</t>
-  </si>
-  <si>
-    <t>Episodic 30-day periods per year</t>
-  </si>
-  <si>
-    <t>1,000/branch x 80 (workbook). Derived alternative is 128,000</t>
-  </si>
-  <si>
-    <t>Total visits per year</t>
-  </si>
-  <si>
-    <t>Estimate: 3,000 clinicians x ~1,000 visits</t>
-  </si>
-  <si>
-    <t>Non-episodic visits per year</t>
-  </si>
-  <si>
-    <t>Estimate from non-FFS revenue</t>
-  </si>
-  <si>
-    <t>B.  UNIT ECONOMICS</t>
-  </si>
-  <si>
-    <t>Contribution per recovered admission</t>
-  </si>
-  <si>
-    <t>8.13 workbook</t>
-  </si>
-  <si>
-    <t>Workbook</t>
-  </si>
-  <si>
-    <t>Revenue protected per avoided LUPA</t>
-  </si>
-  <si>
-    <t>Contribution per non-episodic visit</t>
-  </si>
-  <si>
-    <t>Derived: ~$150 revenue less per-visit pay and variable</t>
-  </si>
-  <si>
-    <t>Modelled</t>
-  </si>
-  <si>
-    <t>Loaded cost per scheduler</t>
-  </si>
-  <si>
-    <t>BLS home health scheduler $38,090 median x 1.43</t>
-  </si>
-  <si>
-    <t>Replacement cost per clinician</t>
-  </si>
-  <si>
-    <t>Clinician departures per branch per year</t>
-  </si>
-  <si>
-    <t>Premium labour pool per branch per year</t>
-  </si>
-  <si>
-    <t>Annual mileage spend, network</t>
-  </si>
-  <si>
-    <t>INVENTED: 3,000 x 8,000 miles x $0.67. Replace</t>
-  </si>
-  <si>
-    <t>Invented</t>
-  </si>
-  <si>
-    <t>C.  SCENARIO DRIVERS</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Mod</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Basis</t>
-  </si>
-  <si>
-    <t>Admission lift</t>
-  </si>
-  <si>
-    <t>LeanTaaS 2% acute; field service 4-15%</t>
-  </si>
-  <si>
-    <t>Fill-rate points recovered, non-episodic</t>
-  </si>
-  <si>
-    <t>Industry fill rates 88-90%</t>
-  </si>
-  <si>
-    <t>LUPA reduction, points of periods</t>
-  </si>
-  <si>
-    <t>8.13 workbook scenario drivers</t>
-  </si>
-  <si>
-    <t>Scheduler FTE released</t>
-  </si>
-  <si>
-    <t>Vendor comparable 27-44; bottom-up build 90</t>
-  </si>
-  <si>
-    <t>Premium labour recovery</t>
-  </si>
-  <si>
-    <t>Clinician turnover reduction</t>
-  </si>
-  <si>
-    <t>8.13 workbook; Bergman 9.2pp worst quartile</t>
-  </si>
-  <si>
-    <t>Travel and mileage reduction</t>
-  </si>
-  <si>
-    <t>Field service 5-15%; UPS ORION 8-10%</t>
-  </si>
-  <si>
-    <t>D.  COST OF OWNERSHIP DRIVERS</t>
-  </si>
-  <si>
-    <t>Implementation and integration (one-time)</t>
-  </si>
-  <si>
-    <t>Data readiness (one-time)</t>
-  </si>
-  <si>
-    <t>Go-live productivity dip (one-time)</t>
-  </si>
-  <si>
-    <t>Software licence (per year)</t>
-  </si>
-  <si>
-    <t>Internal programme labour (per year)</t>
-  </si>
-  <si>
-    <t>Change management (per year)</t>
-  </si>
-  <si>
-    <t>Run and support (per year)</t>
-  </si>
-  <si>
-    <t>Licence is ~10% of total; internal labour ~42%</t>
-  </si>
-  <si>
-    <t>E.  BENEFIT RAMP</t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Share of steady-state benefit realised</t>
-  </si>
-  <si>
-    <t>Phased rollout across ~80 branches</t>
-  </si>
-  <si>
-    <t>Outside-view benefit haircut</t>
-  </si>
-  <si>
-    <t>Set to 56% to apply the McKinsey-Oxford shortfall</t>
-  </si>
-  <si>
-    <t>F.  SCENARIO SELECTOR</t>
-  </si>
-  <si>
-    <t>Scenario driving the Summary sheet</t>
-  </si>
-  <si>
-    <t>Selected scenario</t>
-  </si>
-  <si>
-    <t>Column index (1=Min, 2=Mod, 3=Max)</t>
-  </si>
-  <si>
-    <t>Used by INDEX on the Levers pick</t>
-  </si>
-  <si>
-    <t>Selected COST scenario</t>
-  </si>
-  <si>
-    <t>Set independently of the benefit scenario. An ambitious benefit case does not require an ambitious spend case</t>
-  </si>
-  <si>
-    <t>Cost column index</t>
-  </si>
-  <si>
-    <t>Value levers — annual, at steady state</t>
-  </si>
-  <si>
-    <t>Gross of platform cost. Formulas reference Inputs; edit drivers there, not here.</t>
-  </si>
-  <si>
-    <t>Lever</t>
-  </si>
-  <si>
-    <t>Formula in words</t>
-  </si>
-  <si>
-    <t>1  Speed to answer -&gt; admissions (SOC-capable pool)</t>
-  </si>
-  <si>
-    <t>Admissions x lift x contribution per admission</t>
-  </si>
-  <si>
-    <t>2  Routine throughput and fill rate (paraprofessional pool)</t>
-  </si>
-  <si>
-    <t>Non-episodic visits x fill points x contribution per visit</t>
-  </si>
-  <si>
-    <t>3  LUPA as a scheduling gear</t>
-  </si>
-  <si>
-    <t>Periods x reduction points x revenue protected</t>
-  </si>
-  <si>
-    <t>4  Scheduler capacity released</t>
-  </si>
-  <si>
-    <t>FTE released x loaded cost</t>
-  </si>
-  <si>
-    <t>5  Premium and contract labour recovered</t>
-  </si>
-  <si>
-    <t>Branches x premium pool x recovery rate</t>
-  </si>
-  <si>
-    <t>6  Clinician retention</t>
-  </si>
-  <si>
-    <t>Branches x departures x reduction x replacement cost</t>
-  </si>
-  <si>
-    <t>7  Travel and mileage</t>
-  </si>
-  <si>
-    <t>Mileage spend x reduction rate</t>
-  </si>
-  <si>
-    <t>TOTAL, gross of platform cost</t>
-  </si>
-  <si>
-    <t>Attribution notes</t>
-  </si>
-  <si>
-    <t>- Levers 1 and 2 are separate capacity pools — SOC-capable clinicians and paraprofessionals — and are additive.</t>
-  </si>
-  <si>
-    <t>- Lever 2 is valued on the non-episodic book only. Above the LUPA floor an extra episodic visit earns no revenue.</t>
-  </si>
-  <si>
-    <t>- Lever 3 recovers only clinically indicated visits lost to operational failure. It never adds a visit to clear a threshold.</t>
-  </si>
-  <si>
-    <t>- Lever 7 counts mileage reimbursement only. Under per-visit pay the saved drive time accrues to the clinician, and converts to capacity in lever 1.</t>
-  </si>
-  <si>
-    <t>- Lever 4 excludes severance, which sits on the Cost sheet.</t>
-  </si>
-  <si>
-    <t>Cost of ownership — three years</t>
-  </si>
-  <si>
-    <t>Scenario follows the selector on Inputs B60.</t>
-  </si>
-  <si>
-    <t>Cost line</t>
-  </si>
-  <si>
-    <t>Three-year total</t>
-  </si>
-  <si>
-    <t>Implementation and integration</t>
-  </si>
-  <si>
-    <t>Data readiness</t>
-  </si>
-  <si>
-    <t>Go-live productivity dip</t>
-  </si>
-  <si>
-    <t>Software licence</t>
-  </si>
-  <si>
-    <t>Internal programme labour</t>
-  </si>
-  <si>
-    <t>Change management</t>
-  </si>
-  <si>
-    <t>Run and support</t>
-  </si>
-  <si>
-    <t>Severance on released scheduler roles</t>
-  </si>
-  <si>
-    <t>Assumes 3 months per released role, in year 2</t>
-  </si>
-  <si>
-    <t>TOTAL COST</t>
-  </si>
-  <si>
-    <t>Summary — net position and payback</t>
-  </si>
-  <si>
-    <t>Steady-state benefit, gross</t>
-  </si>
-  <si>
-    <t>Ramp</t>
-  </si>
-  <si>
-    <t>Outside-view haircut</t>
-  </si>
-  <si>
-    <t>Benefit realised</t>
-  </si>
-  <si>
-    <t>Total cost</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>Cumulative net</t>
-  </si>
-  <si>
-    <t>Three-year ROI</t>
-  </si>
-  <si>
-    <t>Payback</t>
-  </si>
-  <si>
-    <t>Steady-state annual benefit, by lever (selected scenario)</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Read this before quoting a number</t>
-  </si>
-  <si>
-    <t>- State the four attribution conventions with any figure: gross or incremental; which revenue base; how many levers; whether config-achievable value counts.</t>
-  </si>
-  <si>
-    <t>- Set the outside-view haircut on Inputs B55 to 56% to see the McKinsey-Oxford expected case.</t>
-  </si>
-  <si>
-    <t>- Three inputs are unresolved and marked yellow. The admissions lever scales linearly with network admissions.</t>
-  </si>
-  <si>
-    <t>Baseline measurement plan</t>
-  </si>
-  <si>
-    <t>Nothing in this model can be committed until these are measured. Ordered by which lever they gate.</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>What it measures</t>
-  </si>
-  <si>
-    <t>Gates which lever</t>
-  </si>
-  <si>
-    <t>Source system</t>
-  </si>
-  <si>
-    <t>Available today</t>
-  </si>
-  <si>
-    <t>How to obtain</t>
-  </si>
-  <si>
-    <t>Effort</t>
-  </si>
-  <si>
     <t>The denominator for every growth claim</t>
   </si>
   <si>
@@ -603,7 +634,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SOC slot utilisation</t>
+    <t>SOC slot utilization</t>
   </si>
   <si>
     <t>SOC-capable capacity offered versus filled, per week</t>
@@ -618,7 +649,7 @@
     <t>Visit fill rate</t>
   </si>
   <si>
-    <t>Authorised and needed visits that go unstaffed, split episodic and non-episodic</t>
+    <t>Authorized and needed visits that go unstaffed, split episodic and non-episodic</t>
   </si>
   <si>
     <t>Lever 2</t>
@@ -627,7 +658,7 @@
     <t>HCHB</t>
   </si>
   <si>
-    <t>Scheduled versus completed versus cancelled, by payer class</t>
+    <t>Scheduled versus completed versus canceled, by payer class</t>
   </si>
   <si>
     <t>Visit mix by discipline</t>
@@ -708,7 +739,7 @@
     <t>Premium, contract and overtime spend</t>
   </si>
   <si>
-    <t>Baseline for the labour recovery lever</t>
+    <t>Baseline for the labor recovery lever</t>
   </si>
   <si>
     <t>Lever 5</t>
@@ -744,10 +775,10 @@
     <t>Computable today from visit records. Validated predictor of quit risk</t>
   </si>
   <si>
-    <t>Income realisation ratio</t>
-  </si>
-  <si>
-    <t>Realised pay against quoted pay at 90 days, per new hire</t>
+    <t>Income realization ratio</t>
+  </si>
+  <si>
+    <t>Realized pay against quoted pay at 90 days, per new hire</t>
   </si>
   <si>
     <t>Payroll + recruiting</t>
@@ -771,7 +802,7 @@
     <t>Replaces the invented mileage figure on Inputs</t>
   </si>
   <si>
-    <t>Authorisation write-offs</t>
+    <t>Authorization write-offs</t>
   </si>
   <si>
     <t>Visits delivered outside the payer backdating window</t>
@@ -786,7 +817,7 @@
     <t>The most under-instrumented dollar in the business. Could be immaterial or the largest single lever</t>
   </si>
   <si>
-    <t>Authorisation turnaround by payer</t>
+    <t>Authorization turnaround by payer</t>
   </si>
   <si>
     <t>Submission to response, by payer and product</t>
@@ -810,13 +841,58 @@
     <t>Confirms the 70% figure and locates the exceptions</t>
   </si>
   <si>
+    <t>Time to fill by discipline</t>
+  </si>
+  <si>
+    <t>Days from requisition to accepted offer</t>
+  </si>
+  <si>
+    <t>Attraction case (future)</t>
+  </si>
+  <si>
+    <t>12 months by discipline and branch. Baseline for the recruiting argument</t>
+  </si>
+  <si>
+    <t>Offer acceptance rate</t>
+  </si>
+  <si>
+    <t>Offers accepted as a share of offers made</t>
+  </si>
+  <si>
+    <t>With decline reasons where captured</t>
+  </si>
+  <si>
+    <t>Cost per hire</t>
+  </si>
+  <si>
+    <t>Recruiting spend per accepted hire, by discipline</t>
+  </si>
+  <si>
+    <t>Finance / HR</t>
+  </si>
+  <si>
+    <t>Needed to value faster filling</t>
+  </si>
+  <si>
+    <t>Exit reason codes</t>
+  </si>
+  <si>
+    <t>Why leavers say they left, coded consistently</t>
+  </si>
+  <si>
+    <t>Levers 6 and attraction</t>
+  </si>
+  <si>
+    <t>Distinguishes schedule and income causes from everything else</t>
+  </si>
+  <si>
     <t>Cost per period by case-mix group</t>
   </si>
   <si>
-    <t>The denominator for the utilisation ceiling</t>
-  </si>
-  <si>
-    <t>Utilisation work</t>
+    <t>The denominator for the utilization ceiling</t>
+  </si>
+  <si>
+    <t>Utilization work</t>
   </si>
   <si>
     <t>Finance</t>
@@ -834,7 +910,148 @@
     <t>- The scheduler task census, pay model split, visit mix, turnover and premium spend together size five of the seven levers.</t>
   </si>
   <si>
-    <t>- By the organisation's own KPI table the initiative's core metric — quantified capacity and utilisation — is not available today, along with 6 of 8 secondary indicators.</t>
+    <t>- By the organization's own KPI table the initiative's core metric — quantified capacity and utilization — is not available today, along with 6 of 8 secondary indicators.</t>
+  </si>
+  <si>
+    <t>Definitions — every term used in this model</t>
+  </si>
+  <si>
+    <t>If a term is not defined here it should not be in the model.</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>What it means, in plain language</t>
+  </si>
+  <si>
+    <t>Why it matters</t>
+  </si>
+  <si>
+    <t>Admissions per year, all branches</t>
+  </si>
+  <si>
+    <t>Every new patient started on service across all 80 branches in a year. A start of care, not a visit and not a referral. One admission generates an episode, which generates one or more payment periods.</t>
+  </si>
+  <si>
+    <t>It is the denominator for the growth lever. The current figure is unresolved and marked yellow.</t>
+  </si>
+  <si>
+    <t>Margin per additional admission</t>
+  </si>
+  <si>
+    <t>The money left over from one more admission after paying the variable costs of delivering it: clinician visit pay, mileage, supplies. It is NOT revenue, and it excludes fixed overhead the branch pays anyway.</t>
+  </si>
+  <si>
+    <t>Growth is only worth what it contributes after variable cost. The workbook uses $1,200.</t>
+  </si>
+  <si>
+    <t>The percentage more admissions we take because capacity is visible and the yes or no arrives faster. 4 percent on 48,000 admissions is about 1,900 more starts a year.</t>
+  </si>
+  <si>
+    <t>Requires referral supply to exist. We currently decline referrals for lack of capacity, so it does.</t>
+  </si>
+  <si>
+    <t>Premium labor</t>
+  </si>
+  <si>
+    <t>Anything paid above the standard rate to get a visit covered: contract and agency clinicians, per diem or PRN at premium rates, overtime, and incentive pay for picking up extra visits. Contract employees are the most expensive tier of it.</t>
+  </si>
+  <si>
+    <t>It is bought reactively today because nobody can see who has room. Forward visibility converts reactive premium coverage into planned coverage.</t>
+  </si>
+  <si>
+    <t>Share of premium labor converted</t>
+  </si>
+  <si>
+    <t>The portion of that premium spend that could have been covered by someone already on the payroll with room in their week, had we been able to see it in time.</t>
+  </si>
+  <si>
+    <t>Not all premium labor is avoidable. Genuine gaps still need contract cover.</t>
+  </si>
+  <si>
+    <t>Fill rate</t>
+  </si>
+  <si>
+    <t>Of the visits that are authorized and clinically needed, the share that actually get staffed and delivered. Industry runs 88 to 90 percent.</t>
+  </si>
+  <si>
+    <t>The gap is revenue on the non-episodic book. Under episodic payment an unfilled routine visit above the floor costs almost nothing.</t>
+  </si>
+  <si>
+    <t>Episodic payment</t>
+  </si>
+  <si>
+    <t>Traditional Medicare. A fixed, case-mix adjusted amount for a 30-day period regardless of how many visits are delivered above the floor.</t>
+  </si>
+  <si>
+    <t>Visits are cost, not revenue. About 47 percent of our book.</t>
+  </si>
+  <si>
+    <t>Non-episodic payment</t>
+  </si>
+  <si>
+    <t>Managed care, commercial and Medicaid. Payment follows the delivered visit or unit, usually with prior authorization and often against an annual cap.</t>
+  </si>
+  <si>
+    <t>Visits are revenue. About 53 percent of our book.</t>
+  </si>
+  <si>
+    <t>LUPA</t>
+  </si>
+  <si>
+    <t>Low Utilization Payment Adjustment. If a 30-day period falls below its case-mix group threshold, 2 to 5 visits, the entire period reprices to national per-visit amounts instead of the full period rate.</t>
+  </si>
+  <si>
+    <t>A cliff of roughly $1,400, not a gradient. Recovery is legitimate only where the visit was clinically indicated and lost to an operational failure.</t>
+  </si>
+  <si>
+    <t>SOC-capable capacity</t>
+  </si>
+  <si>
+    <t>Clinicians qualified and available to admit a new patient, which is a smaller pool than clinicians available for routine visits.</t>
+  </si>
+  <si>
+    <t>It is the binding constraint on growth. A branch can have routine capacity and still be unable to admit.</t>
+  </si>
+  <si>
+    <t>Paraprofessional pool</t>
+  </si>
+  <si>
+    <t>LPNs, PTAs, COTAs and aides, who carry the bulk of weekly routine visit volume.</t>
+  </si>
+  <si>
+    <t>A separate capacity pool from admissions. Their throughput never produces an admission, so the two levers are additive.</t>
+  </si>
+  <si>
+    <t>Revenue for one visit under a per-visit contract, less what we pay the clinician for it and other variable costs. Modeled at $65.</t>
+  </si>
+  <si>
+    <t>The value of each visit recovered through better fill rate.</t>
+  </si>
+  <si>
+    <t>Steady state</t>
+  </si>
+  <si>
+    <t>The annual benefit once the program is fully deployed across all branches, before ramp. Year 3 in this model.</t>
+  </si>
+  <si>
+    <t>Year 1 and 2 are discounted by the ramp on the Inputs sheet.</t>
+  </si>
+  <si>
+    <t>A discount applied to the whole benefit case to reflect that large technology programs typically deliver materially less than predicted. Set it to 56 percent to see the published expected case.</t>
+  </si>
+  <si>
+    <t>Lets the expected case be shown next to the promised case rather than instead of it.</t>
+  </si>
+  <si>
+    <t>Benefit scenario vs cost scenario</t>
+  </si>
+  <si>
+    <t>Two independent selectors. Benefit sets how ambitious the value assumptions are; cost sets how expensive the program is assumed to be.</t>
+  </si>
+  <si>
+    <t>An ambitious benefit case does not require an ambitious spend case. At maximum on both, the program is net negative.</t>
   </si>
 </sst>
 </file>
@@ -939,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -969,6 +1186,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2166,7 +2386,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -2365,28 +2585,84 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="8" t="s">
         <v>130</v>
       </c>
+      <c r="B15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="C16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2405,17 +2681,17 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>95</v>
@@ -2427,12 +2703,12 @@
         <v>97</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B5" s="17">
         <f>INDEX(Inputs!$B$43:$D$43,Inputs!$B$64)</f>
@@ -2451,7 +2727,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B6" s="17">
         <f>INDEX(Inputs!$B$44:$D$44,Inputs!$B$64)</f>
@@ -2470,7 +2746,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B7" s="17">
         <f>INDEX(Inputs!$B$45:$D$45,Inputs!$B$64)</f>
@@ -2489,7 +2765,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B8" s="17">
         <f>INDEX(Inputs!$B$46:$D$46,Inputs!$B$64)</f>
@@ -2510,7 +2786,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B9" s="17">
         <f>INDEX(Inputs!$B$47:$D$47,Inputs!$B$64)</f>
@@ -2531,7 +2807,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B10" s="17">
         <f>INDEX(Inputs!$B$48:$D$48,Inputs!$B$64)</f>
@@ -2552,7 +2828,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B11" s="17">
         <f>INDEX(Inputs!$B$49:$D$49,Inputs!$B$64)</f>
@@ -2573,7 +2849,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B12" s="11">
         <v>0</v>
@@ -2590,12 +2866,12 @@
         <v>900000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B13" s="18">
         <f>SUM(B5:B12)</f>
@@ -2630,7 +2906,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2651,12 +2927,12 @@
         <v>97</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B5" s="17">
         <f>INDEX(Levers!$B$12:$D$12,Inputs!$B$61)</f>
@@ -2673,7 +2949,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B6" s="19">
         <f>Inputs!$B$54</f>
@@ -2690,7 +2966,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B7" s="19">
         <f>Inputs!$B$55</f>
@@ -2707,7 +2983,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B8" s="18">
         <f>B5*B6*(1-B7)</f>
@@ -2728,7 +3004,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B9" s="17">
         <f>Cost!B13</f>
@@ -2749,7 +3025,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B10" s="18">
         <f>B8-B9</f>
@@ -2770,7 +3046,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B11" s="12">
         <f>B10</f>
@@ -2787,7 +3063,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B13" s="20">
         <f>IF(E9=0,0,E10/E9)</f>
@@ -2796,7 +3072,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B14" s="2" t="str">
         <f>IF(D11&gt;0,IF(C11&gt;0,IF(B11&gt;0,"Year 1","Year 2"),"Year 3"),"Beyond year 3")</f>
@@ -2805,7 +3081,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2851,7 +3127,7 @@
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="str">
         <f>Levers!A9</f>
-        <v>5  Premium and contract labour recovered</v>
+        <v>5  Premium and contract labor recovered</v>
       </c>
       <c r="B21" s="17">
         <f>INDEX(Levers!$B$9:$D$9,Inputs!$B$61)</f>
@@ -2880,7 +3156,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B24" s="18">
         <f>SUM(B17:B23)</f>
@@ -2889,22 +3165,22 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +3190,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2928,515 +3204,808 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>189</v>
-      </c>
       <c r="F12" s="21" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="F18" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E24" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F24" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>269</v>
+    </row>
+    <row r="25" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="78" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Business-Case-Model.xlsx
+++ b/agents/compassus-capacity-pm/artifacts/Capacity-Scheduling-Business-Case-Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chigh\flowbuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C19326-4497-4D20-BEF6-110D6F08854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D805A0B-4F52-4C23-804D-462DFE6CD0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,13 +422,13 @@
     <t>The only published figures available: 2 percent in hospitals, 4 to 15 percent in comparable field work</t>
   </si>
   <si>
-    <t>Fewer visits going unstaffed</t>
+    <t>More canceled slots refilled</t>
   </si>
   <si>
     <t>The percentage-point improvement in how many approved, needed visits actually get covered. The industry staffs about 88 to 90 out of every 100.</t>
   </si>
   <si>
-    <t>When a patient cancels or a clinician calls out, the visit is often simply lost because nobody can quickly find who else could take it. On insurers who pay per visit, every one of those is money we had already earned the right to collect.</t>
+    <t>When a patient cancels late, the clinician is left with a gap. Today the branch often cannot find a comparable replacement fast enough for it to fit their day and their driving, so the slot is lost. On insurers who pay per visit, every recovered slot is a visit we get paid for.</t>
   </si>
   <si>
     <t>Published industry staffing rates of 88 to 90 percent</t>
@@ -626,16 +626,16 @@
     <t>Admissions per year, times the percentage increase, times the margin one admission leaves behind</t>
   </si>
   <si>
-    <t>Fewer approved visits going unstaffed</t>
-  </si>
-  <si>
-    <t>When a visit falls through, someone else picks it up quickly instead of it being lost.</t>
-  </si>
-  <si>
-    <t>This is a different group of people from the one above. Aides and assistants carry most of the weekly visits, and their work never produces an admission, so the two do not overlap. On insurers who pay per visit, a visit we could not staff is money we had already earned the right to collect and simply did not.</t>
-  </si>
-  <si>
-    <t>Non-Medicare visits, times the improvement in how many get staffed, times the margin per visit</t>
+    <t>Canceled visits replaced before the day is lost</t>
+  </si>
+  <si>
+    <t>A patient cancels, usually the evening before or the same morning. Rescheduling that patient is handled on the call. What is left is a hole in the clinician's day, and we fill it with a comparable visit fast enough for it to still work.</t>
+  </si>
+  <si>
+    <t>The loss is not the canceled visit, which usually gets rescheduled during the call. The loss is the empty slot left behind. Filling it means knowing instantly who else is due, who is near enough, who is approved, and which visits are flexible enough to move. Sometimes the answer is pulling a visit forward from later in the week, trading a hole we cannot fill today for one we have days to fill. Two things to know: with most clinicians paid per visit, that lost slot is lost income for them, not just for us. And this gets harder as schedules tighten, which is what this system will do, so the replacement ability has to arrive with the optimization rather than after it.</t>
+  </si>
+  <si>
+    <t>Non-Medicare visits, times the improvement in slots recovered, times the margin per visit</t>
   </si>
   <si>
     <t>Fewer Medicare periods falling short on visits</t>
@@ -737,7 +737,7 @@
     <t>The first two rows are different people. Nurses and therapists who admit patients are not the same group as the aides and assistants who carry the routine weekly visits, so both can improve at once without overlapping.</t>
   </si>
   <si>
-    <t>The second row only counts insurers who pay per visit. On traditional Medicare, once the minimum visit count is met, an extra visit brings in nothing, so filling more of them there would be cost without income.</t>
+    <t>The second row only counts insurers who pay per visit. On traditional Medicare, once the minimum visit count is met, an extra visit brings in nothing, so refilling a slot there protects the clinician's income and our coverage, but does not add revenue.</t>
   </si>
   <si>
     <t>What it costs us, over three years</t>
@@ -1812,7 +1812,7 @@
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="str">
         <f>Value!A6</f>
-        <v>Fewer approved visits going unstaffed</v>
+        <v>Canceled visits replaced before the day is lost</v>
       </c>
       <c r="B19" s="6">
         <f>INDEX(Value!$B$6:$D$6,Inputs!$B$56)</f>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F19" s="2" t="str">
         <f>Value!E6</f>
-        <v>When a visit falls through, someone else picks it up quickly instead of it being lost.</v>
+        <v>A patient cancels, usually the evening before or the same morning. Rescheduling that patient is handled on the call. What is left is a hole in the clinician's day, and we fill it with a comparable visit fast enough for it to still work.</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
